--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:50:27+00:00</t>
+    <t>2026-04-07T13:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:39:53+00:00</t>
+    <t>2026-04-08T09:43:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -346,7 +346,7 @@
     <t>fr-lm-entete-document.auteur</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
 </t>
   </si>
   <si>
@@ -785,7 +785,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="76.6640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -343,11 +343,11 @@
     <t>Patient / Usager.</t>
   </si>
   <si>
-    <t>fr-lm-entete-document.auteur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
-</t>
+    <t>fr-lm-entete-document.auteur[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisationhttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device</t>
   </si>
   <si>
     <t>Auteur du document.</t>
@@ -366,7 +366,7 @@
     <t>fr-lm-entete-document.informateur</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
 </t>
   </si>
   <si>
@@ -785,7 +785,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="131.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-entete-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
